--- a/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Composition.xlsx
+++ b/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Composition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2900" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2907" uniqueCount="548">
   <si>
     <t>Property</t>
   </si>
@@ -454,7 +454,7 @@
 </t>
   </si>
   <si>
-    <t>Erweiterungen für die Composition, die durch url unterschieden werden sollen</t>
+    <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>closed</t>
@@ -480,49 +480,52 @@
     <t>Die ID des Begünstigten des E-Rezept-Belegs (z. B. TelematikID der Apotheke)</t>
   </si>
   <si>
+    <t>Composition.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Composition.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Version-independent identifier for the Composition</t>
+  </si>
+  <si>
+    <t>A version-independent identifier for the Composition. This identifier stays constant as the composition is changed over time.</t>
+  </si>
+  <si>
+    <t>Similar to ClinicalDocument/setId in CDA. See discussion in resource definition for how these relate.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>Composition.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Composition.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Version-independent identifier for the Composition</t>
-  </si>
-  <si>
-    <t>A version-independent identifier for the Composition. This identifier stays constant as the composition is changed over time.</t>
-  </si>
-  <si>
-    <t>Similar to ClinicalDocument/setId in CDA. See discussion in resource definition for how these relate.</t>
-  </si>
-  <si>
     <t>Event.identifier</t>
   </si>
   <si>
@@ -646,12 +649,6 @@
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -758,6 +755,9 @@
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
@@ -868,6 +868,10 @@
     <t>Essential metadata for searching for the composition. Identifies who and/or what the composition/document is about.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>.participation[typeCode="SBJ"].role[typeCode="PAT"]</t>
   </si>
   <si>
@@ -893,6 +897,9 @@
     <t>Describes the clinical encounter or type of care this documentation is associated with.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Provides context for the composition and supports searching.</t>
   </si>
   <si>
@@ -1314,6 +1321,14 @@
   </si>
   <si>
     <t>The period of time covered by the documentation. There is no assertion that the documentation is a complete representation for this period, only that it documents events during this time.</t>
+  </si>
+  <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>DocumentReference.event.period</t>
@@ -1475,8 +1490,8 @@
     <t>The root of the sections that make up the composition.</t>
   </si>
   <si>
-    <t>cmp-1:A section must contain at least one of text, entries, or sub-sections {text.exists() or entry.exists() or section.exists()}
-cmp-2:A section can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+cmp-1:A section must contain at least one of text, entries, or sub-sections {text.exists() or entry.exists() or section.exists()}cmp-2:A section can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}</t>
   </si>
   <si>
     <t>./outboundRelationship[typeCode="COMP" and isNormalActRelationship()]/target[moodCode="EVN" and classCode="DOCSECT" and isNormalAct]</t>
@@ -1560,6 +1575,9 @@
     <t>Typically, sections in a doument are about the subject of the document, whether that is a  patient, or group of patients, location, or device, or whatever. For some kind of documents, some sections actually contain data about related entities. Typical examples are  a section in a newborn discharge summary concerning the mother, or family history documents, with a section about each family member, though there are many other examples.</t>
   </si>
   <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
+  </si>
+  <si>
     <t>.subject? (CDA did not differentiate between subject and focus)</t>
   </si>
   <si>
@@ -1573,119 +1591,123 @@
   </si>
   <si>
     <t>Document profiles may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>ele-1
+cmp-1</t>
+  </si>
+  <si>
+    <t>.text</t>
+  </si>
+  <si>
+    <t>Composition.section.mode</t>
+  </si>
+  <si>
+    <t>working | snapshot | changes</t>
+  </si>
+  <si>
+    <t>How the entry list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because a change list must not be misunderstood as a complete list.</t>
+  </si>
+  <si>
+    <t>Sections are used in various ways, and it must be known in what way it is safe to use the entries in them.</t>
+  </si>
+  <si>
+    <t>The processing mode that applies to this section.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-mode|4.0.1</t>
+  </si>
+  <si>
+    <t>.outBoundRelationship[typeCode=COMP].target[classCode=OBS"].value</t>
+  </si>
+  <si>
+    <t>Composition.section.orderedBy</t>
+  </si>
+  <si>
+    <t>Order of section entries</t>
+  </si>
+  <si>
+    <t>Specifies the order applied to the items in the section entries.</t>
+  </si>
+  <si>
+    <t>Applications SHOULD render ordered lists in the order provided, but MAY allow users to re-order based on their own preferences as well. If there is no order specified, the order is unknown, though there may still be some order.</t>
+  </si>
+  <si>
+    <t>Important for presentation and rendering.  Lists may be sorted to place more important information first or to group related entries.</t>
+  </si>
+  <si>
+    <t>What order applies to the items in the entry.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
+  </si>
+  <si>
+    <t>Composition.section.entry</t>
+  </si>
+  <si>
+    <t>A reference to data that supports this section</t>
+  </si>
+  <si>
+    <t>A reference to the actual resource from which the narrative in the section is derived.</t>
+  </si>
+  <si>
+    <t>If there are no entries in the list, an emptyReason SHOULD be provided.</t>
+  </si>
+  <si>
+    <t>ele-1
+cmp-2</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP] or  .participation[typeCode=SBJ]</t>
+  </si>
+  <si>
+    <t>.entry</t>
+  </si>
+  <si>
+    <t>Composition.section.emptyReason</t>
+  </si>
+  <si>
+    <t>Why the section is empty</t>
+  </si>
+  <si>
+    <t>If the section is empty, why the list is empty. An empty section typically has some text explaining the empty reason.</t>
+  </si>
+  <si>
+    <t>The various reasons for an empty section make a significant interpretation to its interpretation. Note that this code is for use when the entire section content has been suppressed, and not for when individual items are omitted - implementers may consider using a text note or a flag on an entry in these cases.</t>
+  </si>
+  <si>
+    <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
+  </si>
+  <si>
+    <t>If a section is empty, why it is empty.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
+  </si>
+  <si>
+    <t>Composition.section.section</t>
+  </si>
+  <si>
+    <t>Nested Section</t>
+  </si>
+  <si>
+    <t>A nested sub-section within this section.</t>
+  </si>
+  <si>
+    <t>Nested sections are primarily used to help human readers navigate to particular portions of the document.</t>
   </si>
   <si>
     <t xml:space="preserve">cmp-1
 </t>
-  </si>
-  <si>
-    <t>.text</t>
-  </si>
-  <si>
-    <t>Composition.section.mode</t>
-  </si>
-  <si>
-    <t>working | snapshot | changes</t>
-  </si>
-  <si>
-    <t>How the entry list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because a change list must not be misunderstood as a complete list.</t>
-  </si>
-  <si>
-    <t>Sections are used in various ways, and it must be known in what way it is safe to use the entries in them.</t>
-  </si>
-  <si>
-    <t>The processing mode that applies to this section.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-mode|4.0.1</t>
-  </si>
-  <si>
-    <t>.outBoundRelationship[typeCode=COMP].target[classCode=OBS"].value</t>
-  </si>
-  <si>
-    <t>Composition.section.orderedBy</t>
-  </si>
-  <si>
-    <t>Order of section entries</t>
-  </si>
-  <si>
-    <t>Specifies the order applied to the items in the section entries.</t>
-  </si>
-  <si>
-    <t>Applications SHOULD render ordered lists in the order provided, but MAY allow users to re-order based on their own preferences as well. If there is no order specified, the order is unknown, though there may still be some order.</t>
-  </si>
-  <si>
-    <t>Important for presentation and rendering.  Lists may be sorted to place more important information first or to group related entries.</t>
-  </si>
-  <si>
-    <t>What order applies to the items in the entry.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
-  </si>
-  <si>
-    <t>Composition.section.entry</t>
-  </si>
-  <si>
-    <t>A reference to data that supports this section</t>
-  </si>
-  <si>
-    <t>A reference to the actual resource from which the narrative in the section is derived.</t>
-  </si>
-  <si>
-    <t>If there are no entries in the list, an emptyReason SHOULD be provided.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cmp-2
-</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP] or  .participation[typeCode=SBJ]</t>
-  </si>
-  <si>
-    <t>.entry</t>
-  </si>
-  <si>
-    <t>Composition.section.emptyReason</t>
-  </si>
-  <si>
-    <t>Why the section is empty</t>
-  </si>
-  <si>
-    <t>If the section is empty, why the list is empty. An empty section typically has some text explaining the empty reason.</t>
-  </si>
-  <si>
-    <t>The various reasons for an empty section make a significant interpretation to its interpretation. Note that this code is for use when the entire section content has been suppressed, and not for when individual items are omitted - implementers may consider using a text note or a flag on an entry in these cases.</t>
-  </si>
-  <si>
-    <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
-  </si>
-  <si>
-    <t>If a section is empty, why it is empty.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
-  </si>
-  <si>
-    <t>Composition.section.section</t>
-  </si>
-  <si>
-    <t>Nested Section</t>
-  </si>
-  <si>
-    <t>A nested sub-section within this section.</t>
-  </si>
-  <si>
-    <t>Nested sections are primarily used to help human readers navigate to particular portions of the document.</t>
   </si>
   <si>
     <t>.component.section</t>
@@ -2040,7 +2062,7 @@
     <col min="26" max="26" width="63.30859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="62.5390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -3207,7 +3229,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>144</v>
@@ -3230,14 +3252,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3259,16 +3281,16 @@
         <v>137</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>79</v>
@@ -3305,16 +3327,16 @@
         <v>79</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>156</v>
@@ -3443,33 +3465,33 @@
         <v>92</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3495,23 +3517,23 @@
         <v>112</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>79</v>
@@ -3529,13 +3551,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3553,7 +3575,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>92</v>
@@ -3568,27 +3590,27 @@
         <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3611,19 +3633,19 @@
         <v>93</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -3651,10 +3673,10 @@
         <v>116</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>79</v>
@@ -3672,7 +3694,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>92</v>
@@ -3681,33 +3703,33 @@
         <v>92</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3730,13 +3752,13 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3787,7 +3809,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3805,7 +3827,7 @@
         <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>79</v>
@@ -3819,14 +3841,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3848,13 +3870,13 @@
         <v>137</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3895,16 +3917,16 @@
         <v>140</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE16" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3922,7 +3944,7 @@
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3936,10 +3958,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3962,19 +3984,19 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3999,29 +4021,29 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4030,7 +4052,7 @@
         <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>104</v>
@@ -4039,7 +4061,7 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -4053,10 +4075,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4079,13 +4101,13 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4136,7 +4158,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4154,7 +4176,7 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -4168,14 +4190,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4197,13 +4219,13 @@
         <v>137</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4244,16 +4266,16 @@
         <v>140</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE19" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4271,7 +4293,7 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4285,10 +4307,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4314,65 +4336,65 @@
         <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4390,7 +4412,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4404,10 +4426,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4430,16 +4452,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4489,7 +4511,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4507,7 +4529,7 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -4521,10 +4543,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4550,63 +4572,63 @@
         <v>112</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="S22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4624,7 +4646,7 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
@@ -4638,10 +4660,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4664,15 +4686,17 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
         <v>239</v>
       </c>
@@ -4900,7 +4924,7 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>252</v>
@@ -5019,7 +5043,7 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>259</v>
@@ -5089,7 +5113,7 @@
         <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>104</v>
@@ -5101,13 +5125,13 @@
         <v>267</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>268</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5208,33 +5232,33 @@
         <v>92</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>275</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5257,17 +5281,19 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5316,7 +5342,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5325,33 +5351,33 @@
         <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>275</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5374,19 +5400,19 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5435,7 +5461,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>92</v>
@@ -5450,27 +5476,27 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5493,17 +5519,19 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5552,7 +5580,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>92</v>
@@ -5561,33 +5589,33 @@
         <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>104</v>
+        <v>275</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5610,16 +5638,16 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5627,7 +5655,7 @@
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>79</v>
@@ -5669,7 +5697,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>92</v>
@@ -5687,13 +5715,13 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5701,10 +5729,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5730,13 +5758,13 @@
         <v>112</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5762,13 +5790,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -5786,7 +5814,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5804,13 +5832,13 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5818,10 +5846,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5844,19 +5872,19 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5905,7 +5933,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5914,7 +5942,7 @@
         <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>104</v>
@@ -5923,13 +5951,13 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5937,10 +5965,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5963,13 +5991,13 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6020,7 +6048,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6038,7 +6066,7 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -6052,14 +6080,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6081,13 +6109,13 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6125,19 +6153,19 @@
         <v>79</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6155,7 +6183,7 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -6169,14 +6197,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6198,16 +6226,16 @@
         <v>137</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N36" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O36" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -6256,7 +6284,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6288,10 +6316,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6317,14 +6345,14 @@
         <v>112</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6349,13 +6377,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6373,7 +6401,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>92</v>
@@ -6391,10 +6419,10 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6405,10 +6433,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6431,17 +6459,17 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6490,7 +6518,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6508,10 +6536,10 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6522,10 +6550,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6548,17 +6576,19 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6607,7 +6637,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6616,33 +6646,33 @@
         <v>92</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>275</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6665,19 +6695,19 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6726,7 +6756,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6735,22 +6765,22 @@
         <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>275</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6758,10 +6788,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6784,16 +6814,16 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6843,7 +6873,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6852,7 +6882,7 @@
         <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>104</v>
@@ -6861,13 +6891,13 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6875,10 +6905,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6901,13 +6931,13 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6958,7 +6988,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6976,7 +7006,7 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
@@ -6990,14 +7020,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7019,13 +7049,13 @@
         <v>137</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7063,19 +7093,19 @@
         <v>79</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7093,7 +7123,7 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
@@ -7107,14 +7137,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7136,16 +7166,16 @@
         <v>137</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N44" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7194,7 +7224,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7226,10 +7256,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7255,13 +7285,13 @@
         <v>112</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7287,13 +7317,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7311,7 +7341,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>92</v>
@@ -7329,13 +7359,13 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7343,10 +7373,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7369,13 +7399,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7426,7 +7456,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>92</v>
@@ -7435,7 +7465,7 @@
         <v>92</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>104</v>
@@ -7444,13 +7474,13 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7458,10 +7488,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7484,19 +7514,19 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7545,7 +7575,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7554,7 +7584,7 @@
         <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>104</v>
@@ -7563,13 +7593,13 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7577,10 +7607,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7603,13 +7633,13 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7660,7 +7690,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7678,7 +7708,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7692,14 +7722,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7721,13 +7751,13 @@
         <v>137</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7765,19 +7795,19 @@
         <v>79</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7795,7 +7825,7 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -7809,14 +7839,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7838,16 +7868,16 @@
         <v>137</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N50" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O50" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7896,7 +7926,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7928,10 +7958,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7954,16 +7984,16 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7992,10 +8022,10 @@
         <v>263</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -8013,7 +8043,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8022,7 +8052,7 @@
         <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>104</v>
@@ -8031,13 +8061,13 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8045,10 +8075,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8071,15 +8101,17 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8128,7 +8160,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8137,22 +8169,22 @@
         <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>424</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8160,10 +8192,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8186,13 +8218,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8243,7 +8275,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8261,7 +8293,7 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -8275,14 +8307,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8304,13 +8336,13 @@
         <v>137</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8351,16 +8383,16 @@
         <v>140</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE54" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8378,7 +8410,7 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
@@ -8392,10 +8424,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8418,16 +8450,16 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8477,7 +8509,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8486,7 +8518,7 @@
         <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -8495,7 +8527,7 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8509,10 +8541,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8535,23 +8567,23 @@
         <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q56" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="R56" t="s" s="2">
         <v>79</v>
@@ -8596,7 +8628,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8605,7 +8637,7 @@
         <v>92</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>104</v>
@@ -8614,7 +8646,7 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8628,10 +8660,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8657,12 +8689,14 @@
         <v>270</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8711,7 +8745,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8720,19 +8754,19 @@
         <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>104</v>
+        <v>275</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>
@@ -8743,10 +8777,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8769,13 +8803,13 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8826,7 +8860,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8844,7 +8878,7 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
@@ -8858,14 +8892,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8887,13 +8921,13 @@
         <v>137</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8934,16 +8968,16 @@
         <v>140</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE59" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8961,7 +8995,7 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
@@ -8975,10 +9009,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9001,16 +9035,16 @@
         <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9060,7 +9094,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9069,7 +9103,7 @@
         <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
@@ -9092,10 +9126,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9121,13 +9155,13 @@
         <v>106</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9153,13 +9187,13 @@
         <v>79</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>79</v>
@@ -9177,7 +9211,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9209,10 +9243,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9238,13 +9272,13 @@
         <v>158</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9294,7 +9328,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9303,7 +9337,7 @@
         <v>92</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>104</v>
@@ -9312,7 +9346,7 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
@@ -9326,10 +9360,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9352,16 +9386,16 @@
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9411,7 +9445,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9443,10 +9477,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9469,13 +9503,13 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9526,7 +9560,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9535,19 +9569,19 @@
         <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>79</v>
@@ -9558,10 +9592,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9584,13 +9618,13 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9641,7 +9675,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9659,7 +9693,7 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
@@ -9673,14 +9707,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9702,13 +9736,13 @@
         <v>137</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9746,19 +9780,19 @@
         <v>79</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9776,7 +9810,7 @@
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>79</v>
@@ -9790,14 +9824,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9819,16 +9853,16 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N67" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O67" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -9877,7 +9911,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9909,14 +9943,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9935,19 +9969,19 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -9996,7 +10030,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10014,10 +10048,10 @@
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>79</v>
@@ -10028,10 +10062,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10054,19 +10088,19 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -10094,10 +10128,10 @@
         <v>263</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>79</v>
@@ -10115,7 +10149,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10124,7 +10158,7 @@
         <v>92</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>104</v>
@@ -10133,10 +10167,10 @@
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>79</v>
@@ -10147,10 +10181,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10173,17 +10207,19 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O70" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>79</v>
@@ -10232,7 +10268,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10241,33 +10277,33 @@
         <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>104</v>
+        <v>275</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10293,13 +10329,13 @@
         <v>270</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10349,7 +10385,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10358,19 +10394,19 @@
         <v>92</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>104</v>
+        <v>275</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>79</v>
+        <v>503</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>79</v>
@@ -10381,10 +10417,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10410,13 +10446,13 @@
         <v>122</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10466,7 +10502,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10475,7 +10511,7 @@
         <v>92</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>104</v>
@@ -10484,10 +10520,10 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>79</v>
@@ -10498,10 +10534,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10527,16 +10563,16 @@
         <v>112</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10561,31 +10597,31 @@
         <v>79</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10603,24 +10639,24 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10643,19 +10679,19 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -10683,29 +10719,29 @@
         <v>116</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>514</v>
-      </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
@@ -10713,7 +10749,7 @@
         <v>92</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>104</v>
@@ -10722,10 +10758,10 @@
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>79</v>
@@ -10736,10 +10772,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10765,13 +10801,13 @@
         <v>270</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10821,7 +10857,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10830,19 +10866,19 @@
         <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>104</v>
+        <v>275</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>79</v>
@@ -10853,10 +10889,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10879,19 +10915,19 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>79</v>
@@ -10919,29 +10955,29 @@
         <v>116</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
@@ -10949,7 +10985,7 @@
         <v>92</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>104</v>
@@ -10958,10 +10994,10 @@
         <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>79</v>
@@ -10972,10 +11008,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11001,13 +11037,13 @@
         <v>82</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11057,7 +11093,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11066,19 +11102,19 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>504</v>
+        <v>546</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>79</v>
